--- a/output/topology_excel/9285.xlsx
+++ b/output/topology_excel/9285.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,202 +490,265 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>40200</v>
+      </c>
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1512</v>
+        <v>71604</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>71604</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>162</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3402</v>
+        <v>224708</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>86</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>89736</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1634</v>
+        <v>420392</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>83</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>420392</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>442</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8398</v>
+        <v>25599</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>81</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>224708</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1328</v>
+        <v>53218</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>81</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>461</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13059</v>
+        <v>53218</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>217409</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1053</v>
+        <v>209289</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>84</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -678,86 +756,113 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1539</v>
+        <v>160477</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>420392</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>411</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11789</v>
+        <v>96612</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>83</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>420392</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1440</v>
+        <v>35888</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>84</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -765,86 +870,113 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>33440</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1872</v>
+        <v>119140</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>80</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>33440</v>
+      </c>
+      <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1428</v>
+        <v>217409</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>418</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>119140</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>419</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9235</v>
+        <v>16767</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>81</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -852,110 +984,146 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>119140</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1869</v>
+        <v>217409</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>147</v>
+      </c>
+      <c r="J15" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>89736</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>324</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6804</v>
+        <v>420392</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>289</v>
+      </c>
+      <c r="J16" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>89736</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2241</v>
+        <v>25599</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>161</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>89736</v>
+      </c>
+      <c r="D18" t="n">
         <v>14</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>290</v>
-      </c>
-      <c r="G18" t="n">
-        <v>11931</v>
+        <v>96612</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>200</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -968,23 +1136,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>420392</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1176</v>
+        <v>25599</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>159</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -997,57 +1174,75 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>420392</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>365</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5398</v>
+        <v>96612</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>227</v>
+      </c>
+      <c r="J20" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>420392</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>80</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1600</v>
+        <v>35888</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>228</v>
+      </c>
+      <c r="J21" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1055,28 +1250,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>418</v>
-      </c>
-      <c r="G22" t="n">
-        <v>13376</v>
+        <v>40200</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>221</v>
+      </c>
+      <c r="J22" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1084,28 +1288,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2106</v>
+        <v>224708</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>316</v>
+      </c>
+      <c r="J23" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1113,86 +1326,113 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>147</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6728</v>
+        <v>53218</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>104</v>
+      </c>
+      <c r="J24" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>92386</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>161</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2576</v>
+        <v>160477</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>324</v>
+      </c>
+      <c r="J25" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>40200</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2600</v>
+        <v>71604</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>162</v>
+      </c>
+      <c r="J26" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1200,28 +1440,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>40200</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>200</v>
-      </c>
-      <c r="G27" t="n">
-        <v>5600</v>
+        <v>224708</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>21</v>
+      </c>
+      <c r="J27" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1229,23 +1478,32 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>40200</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
-      </c>
-      <c r="G28" t="n">
-        <v>11472</v>
+        <v>160477</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>203</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1258,52 +1516,70 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>40200</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
-      </c>
-      <c r="G29" t="n">
-        <v>399</v>
+        <v>53218</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>78</v>
+      </c>
+      <c r="J29" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>71604</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>247</v>
-      </c>
-      <c r="G30" t="n">
-        <v>8151</v>
+        <v>224708</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>442</v>
+      </c>
+      <c r="J30" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1316,86 +1592,113 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>217409</v>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>120</v>
-      </c>
-      <c r="G31" t="n">
-        <v>11640</v>
+        <v>209289</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>480</v>
+      </c>
+      <c r="J31" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>217409</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>179</v>
-      </c>
-      <c r="G32" t="n">
-        <v>8169</v>
+        <v>19019</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>247</v>
+      </c>
+      <c r="J32" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>217409</v>
+      </c>
+      <c r="D33" t="n">
+        <v>18</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>161</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4025</v>
+        <v>47553</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>104</v>
+      </c>
+      <c r="J33" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1403,28 +1706,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>224708</v>
+      </c>
+      <c r="D34" t="n">
+        <v>13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>494</v>
-      </c>
-      <c r="G34" t="n">
-        <v>16302</v>
+        <v>53218</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>350</v>
+      </c>
+      <c r="J34" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1432,57 +1744,75 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>224708</v>
+      </c>
+      <c r="D35" t="n">
         <v>15</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F35" t="n">
-        <v>232</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4872</v>
+        <v>160477</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>231</v>
+      </c>
+      <c r="J35" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>25599</v>
+      </c>
+      <c r="D36" t="n">
         <v>14</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>172</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4644</v>
+        <v>96612</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>161</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1490,28 +1820,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>209289</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3654</v>
+        <v>47553</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>504</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1519,52 +1858,146 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>53218</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>77</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2002</v>
+        <v>160477</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>224</v>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>96612</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>35888</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>172</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>17</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>19019</v>
+      </c>
+      <c r="D40" t="n">
         <v>18</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>47553</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>77</v>
+      </c>
+      <c r="J40" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>18</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>47553</v>
+      </c>
+      <c r="D41" t="n">
         <v>19</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>15939</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
         <v>77</v>
       </c>
-      <c r="G39" t="n">
-        <v>2002</v>
+      <c r="J41" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9285.xlsx
+++ b/output/topology_excel/9285.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1006,10 +1006,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J15" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -1090,26 +1090,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>89736</v>
+        <v>420392</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>96612</v>
+        <v>25599</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="J18" t="n">
         <v>13</v>
@@ -1139,15 +1139,15 @@
         <v>420392</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25599</v>
+        <v>96612</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
@@ -1177,15 +1177,15 @@
         <v>420392</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>96612</v>
+        <v>35888</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J20" t="n">
-        <v>102</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>420392</v>
+        <v>92386</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>35888</v>
+        <v>40200</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="J21" t="n">
-        <v>183</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -1253,7 +1253,7 @@
         <v>92386</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>40200</v>
+        <v>224708</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="J22" t="n">
-        <v>142</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -1291,7 +1291,7 @@
         <v>92386</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>224708</v>
+        <v>53218</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>316</v>
+        <v>104</v>
       </c>
       <c r="J23" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1329,15 +1329,15 @@
         <v>92386</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>53218</v>
+        <v>160477</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,15 +1348,15 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>104</v>
+        <v>324</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1364,18 +1364,18 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>92386</v>
+        <v>40200</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>160477</v>
+        <v>71604</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="J25" t="n">
         <v>21</v>
@@ -1405,15 +1405,15 @@
         <v>40200</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>71604</v>
+        <v>224708</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -1443,7 +1443,7 @@
         <v>40200</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>224708</v>
+        <v>53218</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="J27" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40200</v>
+        <v>71604</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>160477</v>
+        <v>224708</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,26 +1500,26 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>203</v>
+        <v>442</v>
       </c>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40200</v>
+        <v>217409</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>53218</v>
+        <v>209289</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,26 +1538,26 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="J29" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>71604</v>
+        <v>217409</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>224708</v>
+        <v>19019</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>442</v>
+        <v>247</v>
       </c>
       <c r="J30" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -1595,7 +1595,7 @@
         <v>217409</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>209289</v>
+        <v>47553</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,26 +1614,26 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>480</v>
+        <v>104</v>
       </c>
       <c r="J31" t="n">
-        <v>105</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>217409</v>
+        <v>224708</v>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19019</v>
+        <v>53218</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,34 +1652,34 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>247</v>
+        <v>350</v>
       </c>
       <c r="J32" t="n">
-        <v>33</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>217409</v>
+        <v>224708</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>47553</v>
+        <v>160477</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="J33" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>224708</v>
+        <v>25599</v>
       </c>
       <c r="D34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>53218</v>
+        <v>96612</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,15 +1728,15 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="J34" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1744,18 +1744,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>224708</v>
+        <v>209289</v>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>160477</v>
+        <v>47553</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1766,34 +1766,34 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>231</v>
+        <v>504</v>
       </c>
       <c r="J35" t="n">
-        <v>179</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25599</v>
+        <v>53218</v>
       </c>
       <c r="D36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>96612</v>
+        <v>160477</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,15 +1804,15 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="J36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1820,18 +1820,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>209289</v>
+        <v>96612</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>47553</v>
+        <v>35888</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,15 +1842,15 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>504</v>
+        <v>172</v>
       </c>
       <c r="J37" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1858,18 +1858,18 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>53218</v>
+        <v>19019</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>160477</v>
+        <v>47553</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,15 +1880,15 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1896,18 +1896,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>96612</v>
+        <v>47553</v>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>35888</v>
+        <v>15939</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1918,85 +1918,9 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>17</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>19019</v>
-      </c>
-      <c r="D40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>47553</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>77</v>
-      </c>
-      <c r="J40" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>18</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>47553</v>
-      </c>
-      <c r="D41" t="n">
-        <v>19</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>15939</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>77</v>
-      </c>
-      <c r="J41" t="n">
         <v>26</v>
       </c>
     </row>

--- a/output/topology_excel/9285.xlsx
+++ b/output/topology_excel/9285.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>418</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="F16" t="n">
-        <v>269</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>228</v>
+        <v>377</v>
       </c>
       <c r="F20" t="n">
-        <v>183</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>221</v>
+        <v>428</v>
       </c>
       <c r="F21" t="n">
-        <v>142</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -941,12 +941,12 @@
         <v>104</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
         <v>15</v>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="F24" t="n">
         <v>21</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>162</v>
+        <v>442</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="F27" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="n">
         <v>8</v>
       </c>
-      <c r="B28" t="n">
-        <v>10</v>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>442</v>
+        <v>209</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>480</v>
+        <v>172</v>
       </c>
       <c r="F29" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>247</v>
+        <v>418</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="F32" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -1147,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>158</v>
+        <v>324</v>
       </c>
       <c r="F33" t="n">
         <v>21</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="F34" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B35" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>504</v>
+        <v>158</v>
       </c>
       <c r="F35" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="F36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B38" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,32 +1268,274 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" t="n">
+        <v>16</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>108</v>
+      </c>
+      <c r="F39" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>14</v>
+      </c>
+      <c r="B40" t="n">
         <v>18</v>
       </c>
-      <c r="B39" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>104</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="n">
         <v>19</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" t="n">
+        <v>18</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>78</v>
+      </c>
+      <c r="F42" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" t="n">
+        <v>18</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>350</v>
+      </c>
+      <c r="F43" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>504</v>
+      </c>
+      <c r="F44" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>20</v>
+      </c>
+      <c r="B45" t="n">
+        <v>21</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
         <v>77</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F45" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>21</v>
+      </c>
+      <c r="B46" t="n">
+        <v>22</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>77</v>
+      </c>
+      <c r="F46" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>89</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>311</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>271</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>23</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9285.xlsx
+++ b/output/topology_excel/9285.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,42 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
         </is>
       </c>
     </row>
@@ -481,6 +511,12 @@
       <c r="F2" t="n">
         <v>21</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +539,12 @@
       <c r="F3" t="n">
         <v>19</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +567,12 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +595,12 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +623,12 @@
       <c r="F6" t="n">
         <v>19</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +651,12 @@
       <c r="F7" t="n">
         <v>18</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +679,12 @@
       <c r="F8" t="n">
         <v>17</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +707,12 @@
       <c r="F9" t="n">
         <v>21</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +735,12 @@
       <c r="F10" t="n">
         <v>27</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +763,12 @@
       <c r="F11" t="n">
         <v>14</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +791,12 @@
       <c r="F12" t="n">
         <v>25</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +819,12 @@
       <c r="F13" t="n">
         <v>14</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -743,8 +845,14 @@
         <v>169</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -759,14 +867,24 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="F15" t="n">
-        <v>269</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>248</v>
+      </c>
+      <c r="H15" t="n">
+        <v>37</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +907,12 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +935,12 @@
       <c r="F17" t="n">
         <v>25</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +963,12 @@
       <c r="F18" t="n">
         <v>16</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +991,12 @@
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -869,14 +1011,24 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>377</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G20" t="n">
+        <v>225</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -891,14 +1043,24 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>428</v>
+        <v>166</v>
       </c>
       <c r="F21" t="n">
-        <v>105</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G21" t="n">
+        <v>253</v>
+      </c>
+      <c r="H21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1083,12 @@
       <c r="F22" t="n">
         <v>33</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1111,12 @@
       <c r="F23" t="n">
         <v>33</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1139,12 @@
       <c r="F24" t="n">
         <v>21</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1167,12 @@
       <c r="F25" t="n">
         <v>19</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1195,12 @@
       <c r="F26" t="n">
         <v>25</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1223,12 @@
       <c r="F27" t="n">
         <v>27</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1045,14 +1243,24 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
+      <c r="G28" t="n">
+        <v>80</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1283,12 @@
       <c r="F29" t="n">
         <v>27</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1311,12 @@
       <c r="F30" t="n">
         <v>32</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1117,8 +1337,14 @@
         <v>140</v>
       </c>
       <c r="F31" t="n">
-        <v>105</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1367,12 @@
       <c r="F32" t="n">
         <v>24</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1395,12 @@
       <c r="F33" t="n">
         <v>21</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,14 +1415,24 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G34" t="n">
+        <v>203</v>
+      </c>
+      <c r="H34" t="n">
+        <v>21</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1455,12 @@
       <c r="F35" t="n">
         <v>21</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1483,12 @@
       <c r="F36" t="n">
         <v>20</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1511,12 @@
       <c r="F37" t="n">
         <v>26</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1265,14 +1531,24 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="F38" t="n">
-        <v>142</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G38" t="n">
+        <v>114</v>
+      </c>
+      <c r="H38" t="n">
+        <v>21</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1571,12 @@
       <c r="F39" t="n">
         <v>56</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1599,12 @@
       <c r="F40" t="n">
         <v>18</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1627,12 @@
       <c r="F41" t="n">
         <v>19</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1655,12 @@
       <c r="F42" t="n">
         <v>69</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1375,13 +1675,31 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>350</v>
+        <v>105</v>
       </c>
       <c r="F43" t="n">
-        <v>210</v>
+        <v>31</v>
+      </c>
+      <c r="G43" t="n">
+        <v>83</v>
+      </c>
+      <c r="H43" t="n">
+        <v>21</v>
+      </c>
+      <c r="I43" t="n">
+        <v>203</v>
+      </c>
+      <c r="J43" t="n">
+        <v>21</v>
+      </c>
+      <c r="K43" t="n">
+        <v>189</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -1397,14 +1715,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>192</v>
       </c>
       <c r="F44" t="n">
         <v>33</v>
       </c>
+      <c r="G44" t="n">
+        <v>302</v>
+      </c>
+      <c r="H44" t="n">
+        <v>33</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1755,12 @@
       <c r="F45" t="n">
         <v>26</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1783,12 @@
       <c r="F46" t="n">
         <v>26</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1811,12 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1839,12 @@
       <c r="F48" t="n">
         <v>1</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1867,12 @@
       <c r="F49" t="n">
         <v>1</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1895,12 @@
       <c r="F50" t="n">
         <v>1</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
